--- a/hard/hardware.xlsx
+++ b/hard/hardware.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lipoy\Dropbox\develop\Kontengi\ArmillarySphere\hard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89885573-7BC3-4458-855A-0BF35D71731D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5628B7-36FE-4B34-8716-E095F91D52D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -238,35 +238,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>VX07805-500</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DCDCコンバータ 5V 500mA</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>電解コンデンサ 33uF 10V</t>
-    <rPh sb="0" eb="2">
-      <t>デンカイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ショットキーバリアダイオード (汎用品)</t>
-    <rPh sb="16" eb="19">
-      <t>ハンヨウヒン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>NPNデジトラ (汎用品)</t>
-    <rPh sb="9" eb="12">
-      <t>ハンヨウヒン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>100Ω抵抗 (汎用品)</t>
     <rPh sb="4" eb="6">
       <t>テイコウ</t>
@@ -492,6 +463,32 @@
   </si>
   <si>
     <t>カソード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ショットキーバリアダイオード SS2040FL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電解コンデンサ 33uF 10V (汎用品)</t>
+    <rPh sb="0" eb="2">
+      <t>デンカイ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>ハンヨウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BP5293-50</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DCDCコンバータ 5V 1A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NPNデジトラ DTC014EEB</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -621,7 +618,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -653,11 +650,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -677,7 +671,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1212,10 +1205,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="8" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="C13" s="6">
         <v>1</v>
@@ -1223,7 +1216,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="8" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>13</v>
@@ -1234,7 +1227,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="8" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>15</v>
@@ -1245,7 +1238,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="8" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>16</v>
@@ -1256,7 +1249,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="8" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>14</v>
@@ -1273,133 +1266,129 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{891371DF-331D-4A12-8788-744CD64E0AF7}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="19.6640625" customWidth="1"/>
     <col min="4" max="4" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B5" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="17" t="s">
+      <c r="B6" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
+      <c r="C6" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
+      <c r="B7" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>41</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1425,28 +1414,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>62</v>
+        <v>31</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>57</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1454,16 +1443,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="24">
+        <v>65</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="21">
         <v>1</v>
       </c>
-      <c r="E2" s="22" t="s">
-        <v>69</v>
+      <c r="E2" s="19" t="s">
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="str">
         <f>"+12V"</f>
@@ -1475,19 +1464,19 @@
         <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="24">
+        <v>72</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="21">
         <v>2</v>
       </c>
-      <c r="E3" s="22" t="s">
-        <v>50</v>
+      <c r="E3" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1495,19 +1484,19 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="21">
+        <v>3</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="24">
-        <v>3</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1515,19 +1504,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="24">
+        <v>70</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="21">
         <v>4</v>
       </c>
-      <c r="E5" s="22" t="s">
-        <v>67</v>
+      <c r="E5" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1535,20 +1524,20 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="27" t="str">
+        <v>69</v>
+      </c>
+      <c r="C6" s="23" t="str">
         <f>"+3.3V"</f>
         <v>+3.3V</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="21">
         <v>5</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>66</v>
+      <c r="E6" s="19" t="s">
+        <v>61</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1556,20 +1545,20 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="27" t="str">
+        <v>68</v>
+      </c>
+      <c r="C7" s="23" t="str">
         <f>"+3.3V"</f>
         <v>+3.3V</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="21">
         <v>6</v>
       </c>
-      <c r="E7" s="22" t="s">
-        <v>65</v>
+      <c r="E7" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1577,19 +1566,19 @@
         <v>2</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="20">
         <v>7</v>
       </c>
-      <c r="E8" s="20" t="s">
-        <v>63</v>
+      <c r="E8" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1597,19 +1586,19 @@
         <v>1</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="21">
         <v>8</v>
       </c>
-      <c r="E9" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>50</v>
+      <c r="E9" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1632,15 +1621,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1648,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1656,7 +1645,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1664,7 +1653,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1672,20 +1661,20 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1693,7 +1682,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1701,20 +1690,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1731,7 +1720,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1739,7 +1728,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1747,7 +1736,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/hard/hardware.xlsx
+++ b/hard/hardware.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lipoy\Dropbox\develop\Kontengi\ArmillarySphere\hard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5628B7-36FE-4B34-8716-E095F91D52D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BF6A42-F69A-4480-8FDC-35CB66C365F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="部品表" sheetId="4" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="89">
   <si>
     <t>型番</t>
     <rPh sb="0" eb="2">
@@ -489,6 +489,10 @@
   </si>
   <si>
     <t>NPNデジトラ DTC014EEB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>M5Stack Basic</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -496,7 +500,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -517,6 +521,23 @@
       <color theme="10"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -618,7 +639,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -672,6 +693,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1063,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC02FE2-A17A-411D-ABFF-922ED981C218}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="39.83203125" style="10" customWidth="1"/>
@@ -1083,44 +1113,44 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="27">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B4" s="8" t="s">
         <v>3</v>
-      </c>
-      <c r="C3" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="36">
-      <c r="A4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>20</v>
       </c>
       <c r="C4" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" ht="36">
       <c r="A5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>5</v>
+        <v>19</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="C5" s="6">
         <v>2</v>
@@ -1128,21 +1158,21 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
@@ -1150,10 +1180,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C8" s="6">
         <v>1</v>
@@ -1161,10 +1191,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
@@ -1172,32 +1202,32 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="8" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C10" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="8" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C12" s="6">
         <v>1</v>
@@ -1205,10 +1235,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="8" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="C13" s="6">
         <v>1</v>
@@ -1216,10 +1246,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="C14" s="6">
         <v>1</v>
@@ -1227,10 +1257,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" s="6">
         <v>1</v>
@@ -1238,10 +1268,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="6">
         <v>1</v>
@@ -1249,12 +1279,23 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C18" s="6">
         <v>1</v>
       </c>
     </row>
